--- a/data/trans_dic/IP16A03-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A03-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos</t>
+          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 22,22</t>
+          <t>3,75; 21,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,91</t>
+          <t>0,0; 10,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,21</t>
+          <t>0,0; 10,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,7</t>
+          <t>0,0; 20,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,2</t>
+          <t>0,0; 12,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 24,2</t>
+          <t>5,08; 25,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 21,32</t>
+          <t>2,5; 20,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 26,23</t>
+          <t>1,82; 26,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 12,18</t>
+          <t>2,19; 11,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 13,77</t>
+          <t>3,4; 13,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 11,41</t>
+          <t>1,82; 11,89</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 17,44</t>
+          <t>2,12; 17,16</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 12,47</t>
+          <t>1,43; 12,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 10,53</t>
+          <t>1,2; 10,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,18</t>
+          <t>0,0; 8,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,2</t>
+          <t>0,0; 7,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,39; 21,89</t>
+          <t>6,46; 20,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 13,84</t>
+          <t>1,53; 13,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 13,95</t>
+          <t>4,55; 13,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,71</t>
+          <t>0,53; 4,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 8,6</t>
+          <t>0,83; 7,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,78</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,19</t>
+          <t>0,0; 15,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 19,42</t>
+          <t>2,49; 22,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,61</t>
+          <t>0,0; 12,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,32</t>
+          <t>0,0; 14,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,01</t>
+          <t>0,0; 16,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,85</t>
+          <t>0,0; 9,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,32</t>
+          <t>0,0; 10,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,86</t>
+          <t>0,0; 8,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 14,84</t>
+          <t>2,4; 14,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,23</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,47</t>
+          <t>0,0; 7,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 15,81</t>
+          <t>1,73; 15,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,09</t>
+          <t>0,0; 12,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,85</t>
+          <t>0,0; 17,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,43</t>
+          <t>0,0; 6,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 16,88</t>
+          <t>1,82; 17,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,99</t>
+          <t>0,0; 12,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,02</t>
+          <t>0,0; 20,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 11,14</t>
+          <t>1,29; 11,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 13,14</t>
+          <t>2,84; 13,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,84</t>
+          <t>0,0; 7,6</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 13,35</t>
+          <t>0,0; 13,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 5,66</t>
+          <t>0,84; 6,98</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,11; 9,78</t>
+          <t>2,94; 9,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,27; 8,02</t>
+          <t>2,24; 7,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,36</t>
+          <t>0,55; 4,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,48</t>
+          <t>0,44; 4,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,47; 11,22</t>
+          <t>4,23; 11,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,26</t>
+          <t>1,7; 7,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 9,31</t>
+          <t>2,48; 9,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,31</t>
+          <t>1,62; 6,55</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 9,37</t>
+          <t>4,5; 9,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,28</t>
+          <t>2,53; 6,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,68</t>
+          <t>1,95; 5,98</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,52</t>
+          <t>1,35; 4,09</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2796</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4576</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1932</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3523</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5307</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2837</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2698</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1090; 6171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4008</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2816</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3203</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3659</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1954; 9630</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>599; 5014</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>407; 5818</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1286; 6953</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2544; 10338</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>929; 6067</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>811; 6579</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2311</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6185</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2209</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>8225</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2311</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2915</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>783</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>620; 5609</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>647; 5792</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3584</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3659</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3294; 10438</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>658; 5840</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 1655</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>4290; 13115</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>640; 5379</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>709; 6817</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2656</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2844</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3731</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1803</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3451</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>745; 6745</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4594</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3533</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4664</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3065</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4640</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4142</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1388; 8165</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3010</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 6362</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1811</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2858</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2925</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4669</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2244</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3693</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>528; 4671</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3428</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3864</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5306</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>719; 6776</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3116</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4762</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>832; 7336</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1988; 9151</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3954</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6006</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1201; 9958</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>7275</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6564</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2380</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2896</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10465</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>6070</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>6081</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>17740</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>12634</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>8590</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>8977</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>3687; 12295</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3304; 11738</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>696; 5671</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>773; 7380</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6085; 16642</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2685; 12296</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3055; 11275</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2957; 11929</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>12127; 24861</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>7727; 19215</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>4879; 14984</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>4848; 14734</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A03-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A03-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 21,25</t>
+          <t>3,51; 20,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,98</t>
+          <t>0,0; 10,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,42</t>
+          <t>0,0; 10,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,04</t>
+          <t>0,0; 19,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,34</t>
+          <t>0,0; 12,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 25,06</t>
+          <t>5,24; 23,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 20,91</t>
+          <t>2,53; 21,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 26,02</t>
+          <t>1,77; 24,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,19; 11,85</t>
+          <t>2,59; 12,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,4; 13,8</t>
+          <t>2,72; 13,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 11,89</t>
+          <t>1,83; 12,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 17,16</t>
+          <t>2,29; 18,49</t>
         </is>
       </c>
     </row>
@@ -857,27 +857,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 12,98</t>
+          <t>1,44; 12,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 10,79</t>
+          <t>1,19; 11,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,49</t>
+          <t>0,0; 8,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,85</t>
+          <t>0,0; 5,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,46; 20,48</t>
+          <t>5,64; 21,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 13,55</t>
+          <t>1,58; 14,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,38</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 13,93</t>
+          <t>4,94; 14,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,47</t>
+          <t>0,42; 4,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,99</t>
+          <t>0,83; 8,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,78</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,33</t>
+          <t>0,0; 14,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 22,58</t>
+          <t>2,39; 21,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,37</t>
+          <t>0,0; 11,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,81</t>
+          <t>0,0; 14,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,71</t>
+          <t>0,0; 16,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,16</t>
+          <t>0,0; 9,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,05</t>
+          <t>0,0; 8,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,93</t>
+          <t>0,0; 8,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 14,13</t>
+          <t>2,45; 13,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,33</t>
+          <t>0,0; 4,39</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,64</t>
+          <t>0,0; 8,43</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 15,29</t>
+          <t>1,72; 15,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,62</t>
+          <t>0,0; 11,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,51</t>
+          <t>0,0; 15,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,81</t>
+          <t>0,0; 5,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 17,18</t>
+          <t>2,2; 17,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,53</t>
+          <t>0,0; 13,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,93</t>
+          <t>0,0; 21,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 11,34</t>
+          <t>1,22; 11,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 13,08</t>
+          <t>3,02; 13,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,6</t>
+          <t>0,0; 8,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,4</t>
+          <t>1,31; 13,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 6,98</t>
+          <t>0,68; 5,78</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 9,81</t>
+          <t>3,23; 9,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,97</t>
+          <t>2,36; 7,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 4,45</t>
+          <t>0,54; 4,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,15</t>
+          <t>0,46; 4,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 11,56</t>
+          <t>4,39; 11,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 7,78</t>
+          <t>1,85; 7,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,48; 9,15</t>
+          <t>2,6; 9,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,55</t>
+          <t>1,64; 6,33</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 9,23</t>
+          <t>4,38; 9,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,3</t>
+          <t>2,38; 6,3</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,98</t>
+          <t>1,89; 5,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,09</t>
+          <t>1,32; 4,36</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1090; 6171</t>
+          <t>1018; 5874</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4008</t>
+          <t>0; 3703</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2816</t>
+          <t>0; 2873</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3203</t>
+          <t>0; 3146</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3659</t>
+          <t>0; 3656</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1954; 9630</t>
+          <t>2015; 9005</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>599; 5014</t>
+          <t>607; 5079</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>407; 5818</t>
+          <t>396; 5548</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1286; 6953</t>
+          <t>1520; 7247</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2544; 10338</t>
+          <t>2034; 10314</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>929; 6067</t>
+          <t>935; 6197</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>811; 6579</t>
+          <t>876; 7089</t>
         </is>
       </c>
     </row>
@@ -1853,27 +1853,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>620; 5609</t>
+          <t>623; 5369</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>647; 5792</t>
+          <t>638; 5935</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3584</t>
+          <t>0; 3684</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3659</t>
+          <t>0; 2793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3294; 10438</t>
+          <t>2873; 11045</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1883,32 +1883,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>658; 5840</t>
+          <t>682; 6102</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1655</t>
+          <t>0; 1578</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4290; 13115</t>
+          <t>4651; 13355</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>640; 5379</t>
+          <t>502; 5629</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>709; 6817</t>
+          <t>709; 6979</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 2656</t>
+          <t>0; 2805</t>
         </is>
       </c>
     </row>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3451</t>
+          <t>0; 3170</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>745; 6745</t>
+          <t>714; 6555</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2076,47 +2076,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4594</t>
+          <t>0; 4455</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3533</t>
+          <t>0; 3414</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4664</t>
+          <t>0; 4670</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3065</t>
+          <t>0; 3052</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4640</t>
+          <t>0; 4137</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4142</t>
+          <t>0; 3925</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1388; 8165</t>
+          <t>1417; 8063</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3010</t>
+          <t>0; 3052</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 6362</t>
+          <t>0; 7026</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>528; 4671</t>
+          <t>526; 4877</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3428</t>
+          <t>0; 3090</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3864</t>
+          <t>0; 3520</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5306</t>
+          <t>0; 4519</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>719; 6776</t>
+          <t>868; 6768</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3116</t>
+          <t>0; 3307</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4762</t>
+          <t>0; 4944</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>832; 7336</t>
+          <t>787; 7492</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1988; 9151</t>
+          <t>2110; 9460</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 3954</t>
+          <t>0; 4401</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 6006</t>
+          <t>588; 5883</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1201; 9958</t>
+          <t>974; 8244</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3687; 12295</t>
+          <t>4042; 12371</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3304; 11738</t>
+          <t>3480; 11430</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>696; 5671</t>
+          <t>693; 5733</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>773; 7380</t>
+          <t>818; 7824</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6085; 16642</t>
+          <t>6322; 17167</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2685; 12296</t>
+          <t>2916; 11872</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3055; 11275</t>
+          <t>3205; 11629</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2957; 11929</t>
+          <t>2987; 11528</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12127; 24861</t>
+          <t>11788; 25026</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7727; 19215</t>
+          <t>7275; 19237</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4879; 14984</t>
+          <t>4736; 14087</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4848; 14734</t>
+          <t>4735; 15681</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A03-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP16A03-Edad-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9,63%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,36%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 20,23</t>
+          <t>0,0; 12,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,15</t>
+          <t>5,11; 24,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,63</t>
+          <t>2,42; 21,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,68</t>
+          <t>1,75; 16,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,33</t>
+          <t>3,66; 22,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 23,43</t>
+          <t>0,0; 9,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 21,19</t>
+          <t>0,0; 12,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 24,82</t>
+          <t>0,0; 25,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 12,35</t>
+          <t>2,12; 12,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 13,77</t>
+          <t>2,81; 13,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 12,15</t>
+          <t>2,08; 11,41</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 18,49</t>
+          <t>1,15; 14,8</t>
         </is>
       </c>
     </row>
@@ -789,44 +789,44 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12,14%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,72%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,31%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>12,14%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>8,73%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,42</t>
+          <t>6,39; 21,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 11,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,72</t>
+          <t>1,6; 13,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,99</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 21,67</t>
+          <t>1,42; 12,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,22; 10,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 14,16</t>
+          <t>0,0; 9,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 4,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,94; 14,18</t>
+          <t>5,07; 13,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,67</t>
+          <t>0,55; 4,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,18</t>
+          <t>0,84; 8,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2,79%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,52%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,09</t>
+          <t>0,0; 17,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 21,95</t>
+          <t>0,0; 13,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 7,85</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 10,3</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 17,19</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2,38; 19,42</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,99</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 14,31</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 16,73</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,12</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,96</t>
+          <t>0,0; 8,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,46</t>
+          <t>0,0; 8,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 13,95</t>
+          <t>2,43; 14,84</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,39</t>
+          <t>0,0; 4,23</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,43</t>
+          <t>0,0; 7,12</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>5,93%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,5%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,47%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,5%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 15,97</t>
+          <t>1,83; 16,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,37</t>
+          <t>0,0; 9,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,95</t>
+          <t>0,0; 23,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,8</t>
+          <t>1,02; 11,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 17,16</t>
+          <t>1,71; 15,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,3</t>
+          <t>0,0; 12,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,73</t>
+          <t>0,0; 16,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 11,58</t>
+          <t>0,0; 7,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 13,52</t>
+          <t>2,75; 13,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,46</t>
+          <t>0,0; 8,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 13,12</t>
+          <t>1,28; 13,35</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,78</t>
+          <t>1,14; 6,82</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>5,81%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,46%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,87</t>
+          <t>4,47; 11,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,36; 7,76</t>
+          <t>1,67; 7,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,5</t>
+          <t>2,51; 9,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,4</t>
+          <t>1,48; 6,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,39; 11,93</t>
+          <t>3,11; 9,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,52</t>
+          <t>2,27; 8,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 9,43</t>
+          <t>0,55; 4,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,33</t>
+          <t>0,53; 4,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,38; 9,3</t>
+          <t>4,42; 9,37</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,3</t>
+          <t>2,62; 6,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 5,62</t>
+          <t>1,74; 5,68</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,36</t>
+          <t>1,4; 4,55</t>
         </is>
       </c>
     </row>
@@ -1387,13 +1387,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos reconstituyentes como vitaminas, minerales, tónicos (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4576</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2796</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>731</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>910</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4576</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1928</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>814</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>1868</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1018; 5874</t>
+          <t>0; 3617</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3703</t>
+          <t>1964; 9298</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2873</t>
+          <t>580; 5112</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3146</t>
+          <t>305; 2820</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3656</t>
+          <t>1061; 6451</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2015; 9005</t>
+          <t>0; 3616</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>607; 5079</t>
+          <t>0; 3301</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>396; 5548</t>
+          <t>0; 3607</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1520; 7247</t>
+          <t>1244; 7150</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2034; 10314</t>
+          <t>2109; 10317</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>935; 6197</t>
+          <t>1063; 5822</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>876; 7089</t>
+          <t>365; 4677</t>
         </is>
       </c>
     </row>
@@ -1717,37 +1717,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6185</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2209</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2040</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2311</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>705</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6185</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2209</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>366</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>637</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>623; 5369</t>
+          <t>3258; 11155</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>638; 5935</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3684</t>
+          <t>690; 5964</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2793</t>
+          <t>0; 1339</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2873; 11045</t>
+          <t>615; 5388</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>657; 5651</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>682; 6102</t>
+          <t>0; 3877</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1578</t>
+          <t>0; 2032</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4651; 13355</t>
+          <t>4777; 13142</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>502; 5629</t>
+          <t>661; 5675</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>709; 6979</t>
+          <t>716; 7341</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 2805</t>
+          <t>0; 2258</t>
         </is>
       </c>
     </row>
@@ -1930,32 +1930,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1993,62 +1993,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2844</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>887</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3731</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>3731</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1542</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3170</t>
+          <t>0; 4133</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>714; 6555</t>
+          <t>0; 3632</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0; 2626</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4528</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3869</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>710; 5801</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4455</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3414</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4670</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3052</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4137</t>
+          <t>0; 3341</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3925</t>
+          <t>0; 4108</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1417; 8063</t>
+          <t>1402; 8577</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3052</t>
+          <t>0; 2940</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 7026</t>
+          <t>0; 5836</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2858</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2948</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1811</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>678</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>765</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2858</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1479</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>767</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>3714</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>526; 4877</t>
+          <t>721; 6659</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3090</t>
+          <t>0; 2485</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3520</t>
+          <t>0; 5239</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4519</t>
+          <t>633; 7301</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>868; 6768</t>
+          <t>523; 4828</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3307</t>
+          <t>0; 3285</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4944</t>
+          <t>0; 3719</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>787; 7492</t>
+          <t>0; 3785</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2110; 9460</t>
+          <t>1922; 9198</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 4401</t>
+          <t>0; 4599</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>588; 5883</t>
+          <t>574; 5982</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>974; 8244</t>
+          <t>1285; 7663</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>10465</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6070</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>7275</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>6564</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>2380</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>10465</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>6070</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6210</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>7761</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4042; 12371</t>
+          <t>6438; 16150</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3480; 11430</t>
+          <t>2640; 11462</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>693; 5733</t>
+          <t>3098; 11480</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>818; 7824</t>
+          <t>2440; 10178</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6322; 17167</t>
+          <t>3898; 12252</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2916; 11872</t>
+          <t>3342; 11801</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3205; 11629</t>
+          <t>706; 5554</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2987; 11528</t>
+          <t>763; 6885</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11788; 25026</t>
+          <t>11887; 25235</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7275; 19237</t>
+          <t>8004; 19176</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4736; 14087</t>
+          <t>4362; 14236</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4735; 15681</t>
+          <t>4306; 14012</t>
         </is>
       </c>
     </row>
